--- a/development/rocksdb/self_RD/saved01/structured_log_data.xlsx
+++ b/development/rocksdb/self_RD/saved01/structured_log_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF37"/>
+  <dimension ref="A1:CM37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,342 +511,377 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>RocksDB (None) Number Of Total Memory Usage _out</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve"> (Exist Keys fixed #PQ = 5000)  bloom_memtable_hit_count _out</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Exist Keys fixed #PQ = 5000)  bloom_memtable_miss_count _out</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Exist Keys fixed #PQ = 5000)  bloom_sst_hit_count _out</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Exist Keys fixed #PQ = 5000)  bloom_sst_miss_count _out</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Exist Keys fixed #PQ = 5000)  block_read_count _out</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Exist Keys fixed #PQ = 5000)  block_read_byte _out</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Exist Keys fixed #PQ = 5000)  block_read_time _out</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Exist Keys fixed #PQ = 5000)  block_read_cpu_time _out</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Exist Keys fixed #PQ = 5000)  index_block_read_count _out</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Exist Keys fixed #PQ = 5000)  filter_block_read_count _out</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Exist Keys fixed #PQ = 5000)  get_read_bytes _out</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Exist Keys fixed #PQ = 5000)  bytes_read _out</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Exist Keys fixed #PQ = 5000)  bytes_written _out</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>fixed #PQ = 5000 point_query_time_on_existing_keys_ns_out</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Historcially Exist Keys fixed #PQ = 5000)  bloom_memtable_hit_count _out</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Historcially Exist Keys fixed #PQ = 5000)  bloom_memtable_miss_count _out</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Historcially Exist Keys fixed #PQ = 5000)  bloom_sst_hit_count _out</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Historcially Exist Keys fixed #PQ = 5000)  bloom_sst_miss_count _out</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Historcially Exist Keys fixed #PQ = 5000)  block_read_count _out</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Historcially Exist Keys fixed #PQ = 5000)  block_read_byte _out</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Historcially Exist Keys fixed #PQ = 5000)  block_read_time _out</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Historcially Exist Keys fixed #PQ = 5000)  block_read_cpu_time _out</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Historcially Exist Keys fixed #PQ = 5000)  index_block_read_count _out</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Historcially Exist Keys fixed #PQ = 5000)  filter_block_read_count _out</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Historcially Exist Keys fixed #PQ = 5000)  get_read_bytes _out</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Historcially Exist Keys fixed #PQ = 5000)  bytes_read _out</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Historcially Exist Keys fixed #PQ = 5000)  bytes_written _out</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Currently Deleted Keys fixed #PQ = 100000)  bloom_memtable_hit_count _out</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Currently Deleted Keys fixed #PQ = 100000)  bloom_memtable_miss_count _out</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Currently Deleted Keys fixed #PQ = 100000)  bloom_sst_hit_count _out</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Currently Deleted Keys fixed #PQ = 100000)  bloom_sst_miss_count _out</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Currently Deleted Keys fixed #PQ = 100000)  block_read_count _out</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Currently Deleted Keys fixed #PQ = 100000)  block_read_byte _out</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Currently Deleted Keys fixed #PQ = 100000)  block_read_time _out</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Currently Deleted Keys fixed #PQ = 100000)  block_read_cpu_time _out</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Currently Deleted Keys fixed #PQ = 100000)  index_block_read_count _out</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Currently Deleted Keys fixed #PQ = 100000)  filter_block_read_count _out</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Currently Deleted Keys fixed #PQ = 100000)  get_read_bytes _out</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Currently Deleted Keys fixed #PQ = 100000)  bytes_read _out</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Currently Deleted Keys fixed #PQ = 100000)  bytes_written _out</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>fixed #PQ = 100000 point_query_time_on_currently_deleted_all_ns_out</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Non-inserted Keys fixed #PQ = 5000)  bloom_memtable_hit_count _out</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Non-inserted Keys fixed #PQ = 5000)  bloom_memtable_miss_count _out</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Non-inserted Keys fixed #PQ = 5000)  bloom_sst_hit_count _out</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Non-inserted Keys fixed #PQ = 5000)  bloom_sst_miss_count _out</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Non-inserted Keys fixed #PQ = 5000)  block_read_count _out</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Non-inserted Keys fixed #PQ = 5000)  block_read_byte _out</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Non-inserted Keys fixed #PQ = 5000)  block_read_time _out</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Non-inserted Keys fixed #PQ = 5000)  block_read_cpu_time _out</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Non-inserted Keys fixed #PQ = 5000)  index_block_read_count _out</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Non-inserted Keys fixed #PQ = 5000)  filter_block_read_count _out</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Non-inserted Keys fixed #PQ = 5000)  get_read_bytes _out</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Non-inserted Keys fixed #PQ = 5000)  bytes_read _out</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> (Non-inserted Keys fixed #PQ = 5000)  bytes_written _out</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>all_time_ns _out</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>main after workload insertion complete bloom_memtable_hit_count _out</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>main after workload insertion complete bloom_memtable_miss_count _out</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>main after workload insertion complete bloom_sst_hit_count _out</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>main after workload insertion complete bloom_sst_miss_count _out</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>main after workload insertion complete block_read_count _out</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>main after workload insertion complete block_read_byte _out</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>main after workload insertion complete block_read_time _out</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>main after workload insertion complete block_read_cpu_time _out</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>main after workload insertion complete index_block_read_count _out</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>main after workload insertion complete filter_block_read_count _out</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>main after workload insertion complete get_read_bytes _out</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>main after workload insertion complete bytes_read _out</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>main after workload insertion complete bytes_written _out</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Number Of Total Memory Usage _out</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>Split_ Number Of Total Memory Usage _out</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (Exist Keys fixed #PQ = 5000)   filter false positive rate _out</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (Historcially Exist Keys fixed #PQ = 5000)   filter false positive rate _out</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (Currently Deleted Keys fixed #PQ = 100000)   filter false positive rate _out</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> (Non-inserted Keys fixed #PQ = 5000)   filter false positive rate _out</t>
         </is>
       </c>
     </row>
@@ -857,10 +892,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7334257600</v>
+        <v>18534806635</v>
       </c>
       <c r="C2" t="n">
-        <v>1643100</v>
+        <v>5744010</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -902,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4760</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -911,19 +946,19 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1672</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2189.67</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1672</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>6939115.33</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>199805378.67</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -935,16 +970,16 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>12828010.67</v>
       </c>
       <c r="AD2" t="n">
-        <v>13738949400</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>8627682110</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -953,19 +988,19 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1504</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>2128.67</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1504</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>6217894</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>179470111</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -977,10 +1012,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1543370.67</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>11756398</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -992,19 +1027,19 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>91.67</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>35258</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>239701.33</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>6722982</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -1019,13 +1054,13 @@
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>28588585</v>
       </c>
       <c r="BE2" t="n">
-        <v>47341366100</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>37062260544</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1034,10 +1069,10 @@
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>5383</v>
       </c>
       <c r="BK2" t="n">
         <v>0</v>
@@ -1061,13 +1096,13 @@
         <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>4353878</v>
       </c>
       <c r="BS2" t="n">
-        <v>457986681400</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>303788933661</v>
       </c>
       <c r="BU2" t="n">
         <v>0</v>
@@ -1076,10 +1111,10 @@
         <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>5383</v>
       </c>
       <c r="BY2" t="n">
         <v>0</v>
@@ -1103,8 +1138,17 @@
         <v>0</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
-      </c>
+        <v>4353878</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH2" t="inlineStr"/>
+      <c r="CI2" t="inlineStr"/>
+      <c r="CJ2" t="inlineStr"/>
+      <c r="CK2" t="inlineStr"/>
+      <c r="CL2" t="inlineStr"/>
+      <c r="CM2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1113,10 +1157,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7485004400</v>
+        <v>18628139161</v>
       </c>
       <c r="C3" t="n">
-        <v>1670400</v>
+        <v>5802084</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1157,9 +1201,7 @@
       <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1167,19 +1209,19 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1672</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2189.67</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1672</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>6939115.33</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>197011010</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -1191,16 +1233,16 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>12828010.67</v>
       </c>
       <c r="AD3" t="n">
-        <v>12500269200</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>7207928584</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1209,19 +1251,19 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1504</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>2128.67</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1504</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>6217894</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>176468052</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
@@ -1233,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1543370.67</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>11756398</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1248,19 +1290,19 @@
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>91.67</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>35258</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>239701.33</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>6482489.67</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1275,13 +1317,13 @@
         <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>28588585</v>
       </c>
       <c r="BE3" t="n">
-        <v>34401379200</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>25765966926</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1290,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>5383</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
@@ -1317,13 +1359,13 @@
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>4353878</v>
       </c>
       <c r="BS3" t="n">
-        <v>442231986000</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>285906690079</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
@@ -1332,10 +1374,10 @@
         <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>5383</v>
       </c>
       <c r="BY3" t="n">
         <v>0</v>
@@ -1359,8 +1401,19 @@
         <v>0</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
-      </c>
+        <v>4353878</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>1552</v>
+      </c>
+      <c r="CI3" t="inlineStr"/>
+      <c r="CJ3" t="inlineStr"/>
+      <c r="CK3" t="inlineStr"/>
+      <c r="CL3" t="inlineStr"/>
+      <c r="CM3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1369,10 +1422,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7498621000</v>
+        <v>19619694696</v>
       </c>
       <c r="C4" t="n">
-        <v>1586500</v>
+        <v>5947664</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1413,9 +1466,7 @@
       <c r="P4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1423,19 +1474,19 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1672</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2189.67</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1672</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>6939115.33</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>196411117.33</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -1447,16 +1498,16 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>12828010.67</v>
       </c>
       <c r="AD4" t="n">
-        <v>12293094300</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>7211642219</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1465,19 +1516,19 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1503.67</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1975</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1503.67</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>6216492.67</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>177066416</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -1489,10 +1540,10 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1543370.67</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>11521343</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1504,19 +1555,19 @@
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>10.67</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>4221.33</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>33688</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>898915</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -1531,13 +1582,13 @@
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>33688</v>
       </c>
       <c r="BE4" t="n">
-        <v>1174906300</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>754344415</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1549,7 +1600,7 @@
         <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>678</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
@@ -1576,10 +1627,10 @@
         <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>405777454900</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>254954030467</v>
       </c>
       <c r="BU4" t="n">
         <v>0</v>
@@ -1591,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>678</v>
       </c>
       <c r="BY4" t="n">
         <v>0</v>
@@ -1617,6 +1668,17 @@
       <c r="CF4" t="n">
         <v>0</v>
       </c>
+      <c r="CG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH4" t="inlineStr"/>
+      <c r="CI4" t="n">
+        <v>1632</v>
+      </c>
+      <c r="CJ4" t="inlineStr"/>
+      <c r="CK4" t="inlineStr"/>
+      <c r="CL4" t="inlineStr"/>
+      <c r="CM4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1625,10 +1687,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7597321400</v>
+        <v>18941769582</v>
       </c>
       <c r="C5" t="n">
-        <v>1527600</v>
+        <v>2029208</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -1669,9 +1731,7 @@
       <c r="P5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1679,19 +1739,19 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1672</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2189.67</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1672</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>6939115.33</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>195571845.67</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -1703,16 +1763,16 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>12828010.67</v>
       </c>
       <c r="AD5" t="n">
-        <v>12584106900</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>7223782612</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1721,19 +1781,19 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1504</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>2128.67</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1504</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>6217894</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>175883091.33</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
@@ -1745,10 +1805,10 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1543370.67</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>11756398</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1760,19 +1820,19 @@
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>91.67</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>35258</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>239701.33</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>6757268.33</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -1787,13 +1847,13 @@
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>28588585</v>
       </c>
       <c r="BE5" t="n">
-        <v>35526675600</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>26093603220</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1802,10 +1862,10 @@
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>5383</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
@@ -1829,13 +1889,13 @@
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>4353878</v>
       </c>
       <c r="BS5" t="n">
-        <v>419124490600</v>
+        <v>0</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>285944172683</v>
       </c>
       <c r="BU5" t="n">
         <v>0</v>
@@ -1844,10 +1904,10 @@
         <v>0</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>5383</v>
       </c>
       <c r="BY5" t="n">
         <v>0</v>
@@ -1871,6 +1931,25 @@
         <v>0</v>
       </c>
       <c r="CF5" t="n">
+        <v>4353878</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>6400</v>
+      </c>
+      <c r="CI5" t="inlineStr"/>
+      <c r="CJ5" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="CM5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1881,10 +1960,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7234462700</v>
+        <v>19766944564</v>
       </c>
       <c r="C6" t="n">
-        <v>1895200</v>
+        <v>5709837</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1925,9 +2004,7 @@
       <c r="P6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1935,19 +2012,19 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1672</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2189.67</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1672</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>6939115.33</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>195231762</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1959,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>12828010.67</v>
       </c>
       <c r="AD6" t="n">
-        <v>13038414700</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>7227971887</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1977,19 +2054,19 @@
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1503.67</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1976</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1503.67</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>6216492.67</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>175100327.67</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
@@ -2001,10 +2078,10 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1543370.67</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>11522877.67</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2016,19 +2093,19 @@
         <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>10.67</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>4547.33</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>33688</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>847218.67</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -2043,13 +2120,13 @@
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>359703</v>
       </c>
       <c r="BE6" t="n">
-        <v>1816902600</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1186977527</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -2061,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>678</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
@@ -2088,10 +2165,10 @@
         <v>0</v>
       </c>
       <c r="BS6" t="n">
-        <v>433298304600</v>
+        <v>0</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>256559581744</v>
       </c>
       <c r="BU6" t="n">
         <v>0</v>
@@ -2103,7 +2180,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>678</v>
       </c>
       <c r="BY6" t="n">
         <v>0</v>
@@ -2127,6 +2204,25 @@
         <v>0</v>
       </c>
       <c r="CF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>6560</v>
+      </c>
+      <c r="CI6" t="inlineStr"/>
+      <c r="CJ6" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="CM6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2137,10 +2233,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7377845700</v>
+        <v>17353863531</v>
       </c>
       <c r="C7" t="n">
-        <v>1680500</v>
+        <v>6011545</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -2181,9 +2277,7 @@
       <c r="P7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -2191,19 +2285,19 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1672</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2189.67</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1672</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>6939115.33</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>195561104</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -2215,16 +2309,16 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>12828010.67</v>
       </c>
       <c r="AD7" t="n">
-        <v>15034217100</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>7258731016</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -2233,19 +2327,19 @@
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1503.67</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1953</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1503.67</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>6216492.67</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>175214923.67</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -2257,10 +2351,10 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1543370.67</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>11511708.67</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2302,10 +2396,10 @@
         <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1104269700</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>749853598</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2344,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>398078116000</v>
+        <v>0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>262205794243</v>
       </c>
       <c r="BU7" t="n">
         <v>0</v>
@@ -2385,6 +2479,17 @@
       <c r="CF7" t="n">
         <v>0</v>
       </c>
+      <c r="CG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>1632</v>
+      </c>
+      <c r="CI7" t="inlineStr"/>
+      <c r="CJ7" t="inlineStr"/>
+      <c r="CK7" t="inlineStr"/>
+      <c r="CL7" t="inlineStr"/>
+      <c r="CM7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2393,10 +2498,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7335132400</v>
+        <v>20208429034</v>
       </c>
       <c r="C8" t="n">
-        <v>1618600</v>
+        <v>5743381</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -2437,9 +2542,7 @@
       <c r="P8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2447,19 +2550,19 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1672</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2189.67</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1672</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>6939115.33</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>195875256</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -2471,16 +2574,16 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>12828010.67</v>
       </c>
       <c r="AD8" t="n">
-        <v>13294730400</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>7244314943</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -2489,19 +2592,19 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1504</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>2128.67</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1504</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>6217894</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>175188955.67</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
@@ -2513,10 +2616,10 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1543370.67</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>11756398</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2528,19 +2631,19 @@
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>91.67</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>35258</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>239701.33</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>6387514.33</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -2555,13 +2658,13 @@
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>28588585</v>
       </c>
       <c r="BE8" t="n">
-        <v>36598789700</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>26609676187</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2570,10 +2673,10 @@
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>5383</v>
       </c>
       <c r="BK8" t="n">
         <v>0</v>
@@ -2597,13 +2700,13 @@
         <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>4353878</v>
       </c>
       <c r="BS8" t="n">
-        <v>443810329000</v>
+        <v>0</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>282553939678</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -2612,10 +2715,10 @@
         <v>0</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>5383</v>
       </c>
       <c r="BY8" t="n">
         <v>0</v>
@@ -2639,7 +2742,26 @@
         <v>0</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>4353878</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>1321</v>
+      </c>
+      <c r="CI8" t="inlineStr"/>
+      <c r="CJ8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="9">
@@ -2649,10 +2771,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7428869600</v>
+        <v>20238362870</v>
       </c>
       <c r="C9" t="n">
-        <v>1652700</v>
+        <v>5820662</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -2693,9 +2815,7 @@
       <c r="P9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2703,19 +2823,19 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1672</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2189.67</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1672</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>6939115.33</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>195870950</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -2727,16 +2847,16 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>12828010.67</v>
       </c>
       <c r="AD9" t="n">
-        <v>13331119900</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>7292812196</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -2745,19 +2865,19 @@
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1503.67</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1978.67</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1503.67</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>6216492.67</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>176117156.33</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
@@ -2769,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1543370.67</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>11529135.33</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2784,19 +2904,19 @@
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>10.67</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>4889.67</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>33688</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1065424.33</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -2811,13 +2931,13 @@
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>33688</v>
       </c>
       <c r="BE9" t="n">
-        <v>1697542000</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1202773043</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2829,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>781</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -2856,10 +2976,10 @@
         <v>0</v>
       </c>
       <c r="BS9" t="n">
-        <v>395278288900</v>
+        <v>0</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>255928017589</v>
       </c>
       <c r="BU9" t="n">
         <v>0</v>
@@ -2871,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>781</v>
       </c>
       <c r="BY9" t="n">
         <v>0</v>
@@ -2895,6 +3015,25 @@
         <v>0</v>
       </c>
       <c r="CF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>1338</v>
+      </c>
+      <c r="CI9" t="inlineStr"/>
+      <c r="CJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2905,10 +3044,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7448790600</v>
+        <v>20252688018</v>
       </c>
       <c r="C10" t="n">
-        <v>1636300</v>
+        <v>5776645</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -2949,9 +3088,7 @@
       <c r="P10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2959,19 +3096,19 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1672</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2189.67</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1672</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>6939115.33</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>195535624.33</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -2983,16 +3120,16 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>12828010.67</v>
       </c>
       <c r="AD10" t="n">
-        <v>13831760800</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>7314040052</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -3001,19 +3138,19 @@
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1504</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>2128.67</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1504</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>6217894</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>176237505.67</v>
       </c>
       <c r="AM10" t="n">
         <v>0</v>
@@ -3025,10 +3162,10 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1543370.67</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>11756398</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3040,19 +3177,19 @@
         <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>91.67</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>35258</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>239701.33</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>6672708.67</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
@@ -3067,13 +3204,13 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>28588585</v>
       </c>
       <c r="BE10" t="n">
-        <v>38535199900</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>27342013664</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -3082,10 +3219,10 @@
         <v>0</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>5383</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
@@ -3109,13 +3246,13 @@
         <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>4353878</v>
       </c>
       <c r="BS10" t="n">
-        <v>436336651200</v>
+        <v>0</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>283764702292</v>
       </c>
       <c r="BU10" t="n">
         <v>0</v>
@@ -3124,10 +3261,10 @@
         <v>0</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BX10" t="n">
-        <v>0</v>
+        <v>5383</v>
       </c>
       <c r="BY10" t="n">
         <v>0</v>
@@ -3151,7 +3288,26 @@
         <v>0</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>4353878</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>841</v>
+      </c>
+      <c r="CI10" t="inlineStr"/>
+      <c r="CJ10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
@@ -3161,10 +3317,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7330138500</v>
+        <v>20201080122</v>
       </c>
       <c r="C11" t="n">
-        <v>1848700</v>
+        <v>4545112</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -3205,9 +3361,7 @@
       <c r="P11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -3215,19 +3369,19 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1672</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2189.67</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1672</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>6939115.33</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>195192922</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -3239,16 +3393,16 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>12828010.67</v>
       </c>
       <c r="AD11" t="n">
-        <v>13521493200</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>7374261518</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -3257,19 +3411,19 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1503.67</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1981.33</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1503.67</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>6216492.67</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>175826870.33</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
@@ -3281,10 +3435,10 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1543370.67</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>11534535.67</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3296,19 +3450,19 @@
         <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>10.67</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>5671.67</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>33688</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>950991</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -3323,13 +3477,13 @@
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>887553.67</v>
       </c>
       <c r="BE11" t="n">
-        <v>3130568200</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>2084109077</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -3341,7 +3495,7 @@
         <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>875</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
@@ -3365,13 +3519,13 @@
         <v>0</v>
       </c>
       <c r="BR11" t="n">
-        <v>0</v>
+        <v>50701</v>
       </c>
       <c r="BS11" t="n">
-        <v>398338994700</v>
+        <v>0</v>
       </c>
       <c r="BT11" t="n">
-        <v>0</v>
+        <v>255893492210</v>
       </c>
       <c r="BU11" t="n">
         <v>0</v>
@@ -3383,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>0</v>
+        <v>875</v>
       </c>
       <c r="BY11" t="n">
         <v>0</v>
@@ -3407,7 +3561,26 @@
         <v>0</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>50701</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>848</v>
+      </c>
+      <c r="CI11" t="inlineStr"/>
+      <c r="CJ11" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0.0157</v>
       </c>
     </row>
     <row r="12">
@@ -3417,10 +3590,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7456155700</v>
+        <v>20390564267</v>
       </c>
       <c r="C12" t="n">
-        <v>1682800</v>
+        <v>5250872</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -3461,9 +3634,7 @@
       <c r="P12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3471,19 +3642,19 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1672</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2189.67</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1672</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>6939115.33</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>195370156.67</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -3495,16 +3666,16 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>12828010.67</v>
       </c>
       <c r="AD12" t="n">
-        <v>13494162300</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>7275559994</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -3513,19 +3684,19 @@
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1504</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>2128.67</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1504</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>6217894</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>176082552.67</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
@@ -3537,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1543370.67</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>11756398</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3552,19 +3723,19 @@
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>91.67</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>35258</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>239701.33</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>6795118.33</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
@@ -3579,13 +3750,13 @@
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>28588585</v>
       </c>
       <c r="BE12" t="n">
-        <v>36715907800</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>26868536518</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -3594,10 +3765,10 @@
         <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>5383</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -3621,13 +3792,13 @@
         <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>0</v>
+        <v>4353878</v>
       </c>
       <c r="BS12" t="n">
-        <v>433938518400</v>
+        <v>0</v>
       </c>
       <c r="BT12" t="n">
-        <v>0</v>
+        <v>281538125022</v>
       </c>
       <c r="BU12" t="n">
         <v>0</v>
@@ -3636,10 +3807,10 @@
         <v>0</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BX12" t="n">
-        <v>0</v>
+        <v>5383</v>
       </c>
       <c r="BY12" t="n">
         <v>0</v>
@@ -3663,7 +3834,26 @@
         <v>0</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>4353878</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>1081</v>
+      </c>
+      <c r="CI12" t="inlineStr"/>
+      <c r="CJ12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="13">
@@ -3673,10 +3863,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7398627500</v>
+        <v>19917201340</v>
       </c>
       <c r="C13" t="n">
-        <v>1637700</v>
+        <v>5774224</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -3717,9 +3907,7 @@
       <c r="P13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -3727,19 +3915,19 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1672</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2189.67</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1672</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>6939115.33</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>195163220</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -3751,16 +3939,16 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>12828010.67</v>
       </c>
       <c r="AD13" t="n">
-        <v>13365100300</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>7289696546</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -3769,19 +3957,19 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1503.67</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1979.33</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1503.67</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>6216492.67</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>175457827</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
@@ -3793,10 +3981,10 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1543370.67</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>11530144</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3808,19 +3996,19 @@
         <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>10.67</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>5203</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>33688</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>978806.67</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -3835,13 +4023,13 @@
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>382279.67</v>
       </c>
       <c r="BE13" t="n">
-        <v>2323336700</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1598800351</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3853,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>781</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
@@ -3880,10 +4068,10 @@
         <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>396400167900</v>
+        <v>0</v>
       </c>
       <c r="BT13" t="n">
-        <v>0</v>
+        <v>256226598991</v>
       </c>
       <c r="BU13" t="n">
         <v>0</v>
@@ -3895,7 +4083,7 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>0</v>
+        <v>781</v>
       </c>
       <c r="BY13" t="n">
         <v>0</v>
@@ -3919,6 +4107,25 @@
         <v>0</v>
       </c>
       <c r="CF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>1093</v>
+      </c>
+      <c r="CI13" t="inlineStr"/>
+      <c r="CJ13" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0.009299999999999999</v>
+      </c>
+      <c r="CM13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3929,10 +4136,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7861106500</v>
+        <v>20001399720</v>
       </c>
       <c r="C14" t="n">
-        <v>1615300</v>
+        <v>5788486</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -3974,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3983,19 +4190,19 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1670.33</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1844</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1670.33</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>6928283</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>197751836.33</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -4007,16 +4214,16 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>12366942</v>
       </c>
       <c r="AD14" t="n">
-        <v>12823221000</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>8067814791</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -4025,19 +4232,19 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1028.67</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1667.33</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1028.67</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>4268799.67</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>122172361.33</v>
       </c>
       <c r="AM14" t="n">
         <v>0</v>
@@ -4049,10 +4256,10 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1050616</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>8507365.33</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -4064,19 +4271,19 @@
         <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>50.67</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>28720.33</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>32.67</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>137313</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>4061618.67</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
@@ -4091,13 +4298,13 @@
         <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>27886796.33</v>
       </c>
       <c r="BE14" t="n">
-        <v>42972431400</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>38358168734</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -4109,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>4515</v>
       </c>
       <c r="BK14" t="n">
         <v>0</v>
@@ -4133,13 +4340,13 @@
         <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>3794896</v>
       </c>
       <c r="BS14" t="n">
-        <v>426124897900</v>
+        <v>0</v>
       </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>293620717570</v>
       </c>
       <c r="BU14" t="n">
         <v>0</v>
@@ -4151,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0</v>
+        <v>4515</v>
       </c>
       <c r="BY14" t="n">
         <v>0</v>
@@ -4175,8 +4382,17 @@
         <v>0</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
-      </c>
+        <v>3794896</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH14" t="inlineStr"/>
+      <c r="CI14" t="inlineStr"/>
+      <c r="CJ14" t="inlineStr"/>
+      <c r="CK14" t="inlineStr"/>
+      <c r="CL14" t="inlineStr"/>
+      <c r="CM14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4185,10 +4401,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7655360000</v>
+        <v>17520599775</v>
       </c>
       <c r="C15" t="n">
-        <v>1639500</v>
+        <v>5908059</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -4229,9 +4445,7 @@
       <c r="P15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -4239,19 +4453,19 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1670.33</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1844</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1670.33</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>6928283</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>196639840</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -4263,16 +4477,16 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>12366838.67</v>
       </c>
       <c r="AD15" t="n">
-        <v>12220875800</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>6811561137</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -4281,19 +4495,19 @@
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1028.67</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1667.33</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1028.67</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>4268802.33</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>120638063.33</v>
       </c>
       <c r="AM15" t="n">
         <v>0</v>
@@ -4305,10 +4519,10 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1050616</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>8506799</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -4320,19 +4534,19 @@
         <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>50.67</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>28720.33</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>32.67</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>137326.33</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>3856542</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
@@ -4347,13 +4561,13 @@
         <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>27867366</v>
       </c>
       <c r="BE15" t="n">
-        <v>33727321700</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>27194553335</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -4365,7 +4579,7 @@
         <v>0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>4515</v>
       </c>
       <c r="BK15" t="n">
         <v>0</v>
@@ -4389,13 +4603,13 @@
         <v>0</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>3793052</v>
       </c>
       <c r="BS15" t="n">
-        <v>424124452900</v>
+        <v>0</v>
       </c>
       <c r="BT15" t="n">
-        <v>0</v>
+        <v>284206770519</v>
       </c>
       <c r="BU15" t="n">
         <v>0</v>
@@ -4407,7 +4621,7 @@
         <v>0</v>
       </c>
       <c r="BX15" t="n">
-        <v>0</v>
+        <v>4515</v>
       </c>
       <c r="BY15" t="n">
         <v>0</v>
@@ -4431,8 +4645,19 @@
         <v>0</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
-      </c>
+        <v>3793052</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>1472</v>
+      </c>
+      <c r="CI15" t="inlineStr"/>
+      <c r="CJ15" t="inlineStr"/>
+      <c r="CK15" t="inlineStr"/>
+      <c r="CL15" t="inlineStr"/>
+      <c r="CM15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4441,10 +4666,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7680206100</v>
+        <v>18991123806</v>
       </c>
       <c r="C16" t="n">
-        <v>1662500</v>
+        <v>5698667</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4485,9 +4710,7 @@
       <c r="P16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -4495,19 +4718,19 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1670.33</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1844</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1670.33</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>6928283</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>195083836.67</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -4519,16 +4742,16 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>12366838.67</v>
       </c>
       <c r="AD16" t="n">
-        <v>11913615600</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>6785176236</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -4537,19 +4760,19 @@
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1026.67</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1156</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1026.67</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>4260395.67</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>120342172</v>
       </c>
       <c r="AM16" t="n">
         <v>0</v>
@@ -4561,10 +4784,10 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1050616</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>7614015.33</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4576,19 +4799,19 @@
         <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2015.67</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>4208</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>171461.33</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
@@ -4603,13 +4826,13 @@
         <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4208</v>
       </c>
       <c r="BE16" t="n">
-        <v>1186821300</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>736140223</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -4621,7 +4844,7 @@
         <v>0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="BK16" t="n">
         <v>0</v>
@@ -4648,10 +4871,10 @@
         <v>0</v>
       </c>
       <c r="BS16" t="n">
-        <v>403215242000</v>
+        <v>0</v>
       </c>
       <c r="BT16" t="n">
-        <v>0</v>
+        <v>251106181891</v>
       </c>
       <c r="BU16" t="n">
         <v>0</v>
@@ -4663,7 +4886,7 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="BY16" t="n">
         <v>0</v>
@@ -4689,6 +4912,17 @@
       <c r="CF16" t="n">
         <v>0</v>
       </c>
+      <c r="CG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH16" t="inlineStr"/>
+      <c r="CI16" t="n">
+        <v>1632</v>
+      </c>
+      <c r="CJ16" t="inlineStr"/>
+      <c r="CK16" t="inlineStr"/>
+      <c r="CL16" t="inlineStr"/>
+      <c r="CM16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4697,10 +4931,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7749359600</v>
+        <v>17716929701</v>
       </c>
       <c r="C17" t="n">
-        <v>1685800</v>
+        <v>5863205</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -4741,9 +4975,7 @@
       <c r="P17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -4751,19 +4983,19 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1670.33</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1844</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1670.33</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>6928283</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>196441263</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -4775,16 +5007,16 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>12366838.67</v>
       </c>
       <c r="AD17" t="n">
-        <v>12387288200</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>6849706672</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -4793,19 +5025,19 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1028.67</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1667.33</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1028.67</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>4268802.33</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>120468446.33</v>
       </c>
       <c r="AM17" t="n">
         <v>0</v>
@@ -4817,10 +5049,10 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1050616</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>8506799</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4832,19 +5064,19 @@
         <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>50.67</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>28720.33</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>32.67</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>137326.33</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>3940680.33</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
@@ -4859,13 +5091,13 @@
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>27867366</v>
       </c>
       <c r="BE17" t="n">
-        <v>33244757900</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>28153315774</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4877,7 +5109,7 @@
         <v>0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>4515</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
@@ -4901,13 +5133,13 @@
         <v>0</v>
       </c>
       <c r="BR17" t="n">
-        <v>0</v>
+        <v>3793052</v>
       </c>
       <c r="BS17" t="n">
-        <v>424964962200</v>
+        <v>0</v>
       </c>
       <c r="BT17" t="n">
-        <v>0</v>
+        <v>285404461571</v>
       </c>
       <c r="BU17" t="n">
         <v>0</v>
@@ -4919,7 +5151,7 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>0</v>
+        <v>4515</v>
       </c>
       <c r="BY17" t="n">
         <v>0</v>
@@ -4943,6 +5175,25 @@
         <v>0</v>
       </c>
       <c r="CF17" t="n">
+        <v>3793052</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>7296</v>
+      </c>
+      <c r="CI17" t="inlineStr"/>
+      <c r="CJ17" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="CM17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4953,10 +5204,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7470172400</v>
+        <v>19036143815</v>
       </c>
       <c r="C18" t="n">
-        <v>1568500</v>
+        <v>5850887</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -4997,9 +5248,7 @@
       <c r="P18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -5007,19 +5256,19 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1670.33</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1844</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1670.33</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>6928283</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>195715748</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -5031,16 +5280,16 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>12366838.67</v>
       </c>
       <c r="AD18" t="n">
-        <v>12166463900</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>6870562342</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -5049,19 +5298,19 @@
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1026.67</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1156.33</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1026.67</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>4260395.67</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>120011924</v>
       </c>
       <c r="AM18" t="n">
         <v>0</v>
@@ -5073,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1050616</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>7614977.67</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -5088,19 +5337,19 @@
         <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2089.67</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>4208</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>118013</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
@@ -5115,13 +5364,13 @@
         <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>92598.67</v>
       </c>
       <c r="BE18" t="n">
-        <v>1414406100</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>902239439</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -5133,7 +5382,7 @@
         <v>0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="BK18" t="n">
         <v>0</v>
@@ -5160,10 +5409,10 @@
         <v>0</v>
       </c>
       <c r="BS18" t="n">
-        <v>415153304600</v>
+        <v>0</v>
       </c>
       <c r="BT18" t="n">
-        <v>0</v>
+        <v>252124582468</v>
       </c>
       <c r="BU18" t="n">
         <v>0</v>
@@ -5175,7 +5424,7 @@
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="BY18" t="n">
         <v>0</v>
@@ -5199,6 +5448,25 @@
         <v>0</v>
       </c>
       <c r="CF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>7648</v>
+      </c>
+      <c r="CI18" t="inlineStr"/>
+      <c r="CJ18" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="CM18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5209,10 +5477,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7655925300</v>
+        <v>18487765721</v>
       </c>
       <c r="C19" t="n">
-        <v>1650200</v>
+        <v>5705151</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -5253,9 +5521,7 @@
       <c r="P19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -5263,19 +5529,19 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1670.33</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1844</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1670.33</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>6928283</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>194745901.67</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -5287,16 +5553,16 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>12366838.67</v>
       </c>
       <c r="AD19" t="n">
-        <v>13422244200</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>6797893025</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -5305,19 +5571,19 @@
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1026.67</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1115.67</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1026.67</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>4260395.67</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>119680203.33</v>
       </c>
       <c r="AM19" t="n">
         <v>0</v>
@@ -5329,10 +5595,10 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1050616</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>7562910</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -5374,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1097466400</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>700971247</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -5416,10 +5682,10 @@
         <v>0</v>
       </c>
       <c r="BS19" t="n">
-        <v>390347677300</v>
+        <v>0</v>
       </c>
       <c r="BT19" t="n">
-        <v>0</v>
+        <v>250767508962</v>
       </c>
       <c r="BU19" t="n">
         <v>0</v>
@@ -5457,6 +5723,17 @@
       <c r="CF19" t="n">
         <v>0</v>
       </c>
+      <c r="CG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>1536</v>
+      </c>
+      <c r="CI19" t="inlineStr"/>
+      <c r="CJ19" t="inlineStr"/>
+      <c r="CK19" t="inlineStr"/>
+      <c r="CL19" t="inlineStr"/>
+      <c r="CM19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5465,10 +5742,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7711450600</v>
+        <v>19445221409</v>
       </c>
       <c r="C20" t="n">
-        <v>1775400</v>
+        <v>5869446</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -5509,9 +5786,7 @@
       <c r="P20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -5519,19 +5794,19 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1670.33</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1844</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1670.33</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>6928283</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>194663744.33</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -5543,16 +5818,16 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>12366838.67</v>
       </c>
       <c r="AD20" t="n">
-        <v>13261059300</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>6937152007</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -5561,19 +5836,19 @@
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1028.67</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1667.33</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1028.67</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>4268802.33</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>119652231.67</v>
       </c>
       <c r="AM20" t="n">
         <v>0</v>
@@ -5585,10 +5860,10 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1050616</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>8506799</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -5600,19 +5875,19 @@
         <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>50.67</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>28720.33</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>32.67</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>137326.33</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>3750834</v>
       </c>
       <c r="AZ20" t="n">
         <v>0</v>
@@ -5627,13 +5902,13 @@
         <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>27867366</v>
       </c>
       <c r="BE20" t="n">
-        <v>36876676500</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>28526297662</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -5645,7 +5920,7 @@
         <v>0</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>4515</v>
       </c>
       <c r="BK20" t="n">
         <v>0</v>
@@ -5669,13 +5944,13 @@
         <v>0</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>3793052</v>
       </c>
       <c r="BS20" t="n">
-        <v>427907405300</v>
+        <v>0</v>
       </c>
       <c r="BT20" t="n">
-        <v>0</v>
+        <v>281030086583</v>
       </c>
       <c r="BU20" t="n">
         <v>0</v>
@@ -5687,7 +5962,7 @@
         <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>0</v>
+        <v>4515</v>
       </c>
       <c r="BY20" t="n">
         <v>0</v>
@@ -5711,7 +5986,26 @@
         <v>0</v>
       </c>
       <c r="CF20" t="n">
-        <v>0</v>
+        <v>3793052</v>
+      </c>
+      <c r="CG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH20" t="n">
+        <v>1615</v>
+      </c>
+      <c r="CI20" t="inlineStr"/>
+      <c r="CJ20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CK20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="21">
@@ -5721,10 +6015,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7802204600</v>
+        <v>19324193512</v>
       </c>
       <c r="C21" t="n">
-        <v>1662200</v>
+        <v>5759999</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -5765,9 +6059,7 @@
       <c r="P21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -5775,19 +6067,19 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1670.33</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1844</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1670.33</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>6928283</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>195532410.33</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -5799,16 +6091,16 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>12366838.67</v>
       </c>
       <c r="AD21" t="n">
-        <v>13394144800</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>6881405804</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -5817,19 +6109,19 @@
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1026.67</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1190.67</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1026.67</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>4260395.67</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>119760189</v>
       </c>
       <c r="AM21" t="n">
         <v>0</v>
@@ -5841,10 +6133,10 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1050616</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>7671987</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -5856,19 +6148,19 @@
         <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>4008</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>9815.33</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>344154.67</v>
       </c>
       <c r="AZ21" t="n">
         <v>0</v>
@@ -5883,13 +6175,13 @@
         <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>9815.33</v>
       </c>
       <c r="BE21" t="n">
-        <v>3105364400</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1142004704</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5901,7 +6193,7 @@
         <v>0</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0</v>
+        <v>433</v>
       </c>
       <c r="BK21" t="n">
         <v>0</v>
@@ -5928,10 +6220,10 @@
         <v>0</v>
       </c>
       <c r="BS21" t="n">
-        <v>392358714800</v>
+        <v>0</v>
       </c>
       <c r="BT21" t="n">
-        <v>0</v>
+        <v>250896518993</v>
       </c>
       <c r="BU21" t="n">
         <v>0</v>
@@ -5943,7 +6235,7 @@
         <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>0</v>
+        <v>433</v>
       </c>
       <c r="BY21" t="n">
         <v>0</v>
@@ -5967,6 +6259,25 @@
         <v>0</v>
       </c>
       <c r="CF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH21" t="n">
+        <v>1687</v>
+      </c>
+      <c r="CI21" t="inlineStr"/>
+      <c r="CJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5977,10 +6288,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7853170500</v>
+        <v>19359664776</v>
       </c>
       <c r="C22" t="n">
-        <v>1742100</v>
+        <v>5786324</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -6021,9 +6332,7 @@
       <c r="P22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -6031,19 +6340,19 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1670.33</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1844</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1670.33</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>6928283</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>194166110</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -6055,16 +6364,16 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>12366838.67</v>
       </c>
       <c r="AD22" t="n">
-        <v>13718347600</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>6875133627</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -6073,19 +6382,19 @@
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1028.67</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1667.33</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1028.67</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>4268802.33</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>120823675.67</v>
       </c>
       <c r="AM22" t="n">
         <v>0</v>
@@ -6097,10 +6406,10 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1050616</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>8506799</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -6112,19 +6421,19 @@
         <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>50.67</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>28720.33</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>32.67</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>137326.33</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>3809953</v>
       </c>
       <c r="AZ22" t="n">
         <v>0</v>
@@ -6139,13 +6448,13 @@
         <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>27867366</v>
       </c>
       <c r="BE22" t="n">
-        <v>45720622200</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>29333022095</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -6157,7 +6466,7 @@
         <v>0</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0</v>
+        <v>4515</v>
       </c>
       <c r="BK22" t="n">
         <v>0</v>
@@ -6181,13 +6490,13 @@
         <v>0</v>
       </c>
       <c r="BR22" t="n">
-        <v>0</v>
+        <v>3793052</v>
       </c>
       <c r="BS22" t="n">
-        <v>440481022400</v>
+        <v>0</v>
       </c>
       <c r="BT22" t="n">
-        <v>0</v>
+        <v>281886203958</v>
       </c>
       <c r="BU22" t="n">
         <v>0</v>
@@ -6199,7 +6508,7 @@
         <v>0</v>
       </c>
       <c r="BX22" t="n">
-        <v>0</v>
+        <v>4515</v>
       </c>
       <c r="BY22" t="n">
         <v>0</v>
@@ -6223,7 +6532,26 @@
         <v>0</v>
       </c>
       <c r="CF22" t="n">
-        <v>0</v>
+        <v>3793052</v>
+      </c>
+      <c r="CG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH22" t="n">
+        <v>1075</v>
+      </c>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CK22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CL22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="23">
@@ -6233,10 +6561,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7846771900</v>
+        <v>19175346501</v>
       </c>
       <c r="C23" t="n">
-        <v>1559500</v>
+        <v>5740909</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -6277,9 +6605,7 @@
       <c r="P23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -6287,19 +6613,19 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1670.33</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1844</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1670.33</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>6928283</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>195009134</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -6311,16 +6637,16 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>12366838.67</v>
       </c>
       <c r="AD23" t="n">
-        <v>14601692000</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>6883901849</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -6329,19 +6655,19 @@
         <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1026.67</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1192.67</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1026.67</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>4260395.67</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>119141277.67</v>
       </c>
       <c r="AM23" t="n">
         <v>0</v>
@@ -6353,10 +6679,10 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1050616</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>7676647.33</v>
       </c>
       <c r="AR23" t="n">
         <v>0</v>
@@ -6368,19 +6694,19 @@
         <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>4167.67</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>9815.33</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>287522.33</v>
       </c>
       <c r="AZ23" t="n">
         <v>0</v>
@@ -6395,13 +6721,13 @@
         <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>271600</v>
       </c>
       <c r="BE23" t="n">
-        <v>3385444200</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1467623562</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -6413,7 +6739,7 @@
         <v>0</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="BK23" t="n">
         <v>0</v>
@@ -6440,10 +6766,10 @@
         <v>0</v>
       </c>
       <c r="BS23" t="n">
-        <v>396819712200</v>
+        <v>0</v>
       </c>
       <c r="BT23" t="n">
-        <v>0</v>
+        <v>251710155320</v>
       </c>
       <c r="BU23" t="n">
         <v>0</v>
@@ -6455,7 +6781,7 @@
         <v>0</v>
       </c>
       <c r="BX23" t="n">
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="BY23" t="n">
         <v>0</v>
@@ -6480,6 +6806,25 @@
       </c>
       <c r="CF23" t="n">
         <v>0</v>
+      </c>
+      <c r="CG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH23" t="n">
+        <v>1096</v>
+      </c>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="CK23" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="CL23" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>0.0025</v>
       </c>
     </row>
     <row r="24">
@@ -6489,10 +6834,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7730005000</v>
+        <v>19653201080</v>
       </c>
       <c r="C24" t="n">
-        <v>1628300</v>
+        <v>5848012</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -6533,9 +6878,7 @@
       <c r="P24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -6543,19 +6886,19 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1670.33</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1844</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1670.33</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>6928283</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>195021705.67</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -6567,16 +6910,16 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>12366838.67</v>
       </c>
       <c r="AD24" t="n">
-        <v>13481608300</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>6881008324</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -6585,19 +6928,19 @@
         <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1028.67</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1667.33</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1028.67</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>4268802.33</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>120401196.33</v>
       </c>
       <c r="AM24" t="n">
         <v>0</v>
@@ -6609,10 +6952,10 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1050616</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>8506799</v>
       </c>
       <c r="AR24" t="n">
         <v>0</v>
@@ -6624,19 +6967,19 @@
         <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>50.67</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>28720.33</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>32.67</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>137326.33</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>3697047.33</v>
       </c>
       <c r="AZ24" t="n">
         <v>0</v>
@@ -6651,13 +6994,13 @@
         <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>27867366</v>
       </c>
       <c r="BE24" t="n">
-        <v>39121784200</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>28590607835</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -6669,7 +7012,7 @@
         <v>0</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0</v>
+        <v>4515</v>
       </c>
       <c r="BK24" t="n">
         <v>0</v>
@@ -6693,13 +7036,13 @@
         <v>0</v>
       </c>
       <c r="BR24" t="n">
-        <v>0</v>
+        <v>3793052</v>
       </c>
       <c r="BS24" t="n">
-        <v>433154665600</v>
+        <v>0</v>
       </c>
       <c r="BT24" t="n">
-        <v>0</v>
+        <v>280316206975</v>
       </c>
       <c r="BU24" t="n">
         <v>0</v>
@@ -6711,7 +7054,7 @@
         <v>0</v>
       </c>
       <c r="BX24" t="n">
-        <v>0</v>
+        <v>4515</v>
       </c>
       <c r="BY24" t="n">
         <v>0</v>
@@ -6735,7 +7078,26 @@
         <v>0</v>
       </c>
       <c r="CF24" t="n">
-        <v>0</v>
+        <v>3793052</v>
+      </c>
+      <c r="CG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH24" t="n">
+        <v>1345</v>
+      </c>
+      <c r="CI24" t="inlineStr"/>
+      <c r="CJ24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CK24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CL24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CM24" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="25">
@@ -6745,10 +7107,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7524723400</v>
+        <v>19573872190</v>
       </c>
       <c r="C25" t="n">
-        <v>1894600</v>
+        <v>5917222</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -6789,9 +7151,7 @@
       <c r="P25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -6799,19 +7159,19 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1670.33</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1844</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1670.33</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>6928283</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>196217435.33</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -6823,16 +7183,16 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>12366838.67</v>
       </c>
       <c r="AD25" t="n">
-        <v>12249314300</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>6852771697</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -6841,19 +7201,19 @@
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1026.67</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1191</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1026.67</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>4260395.67</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>120314861.67</v>
       </c>
       <c r="AM25" t="n">
         <v>0</v>
@@ -6865,10 +7225,10 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1050616</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>7672949.33</v>
       </c>
       <c r="AR25" t="n">
         <v>0</v>
@@ -6880,19 +7240,19 @@
         <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>4073</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>9815.33</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>281407.33</v>
       </c>
       <c r="AZ25" t="n">
         <v>0</v>
@@ -6907,13 +7267,13 @@
         <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>117299.67</v>
       </c>
       <c r="BE25" t="n">
-        <v>3221148200</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1307963165</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -6925,7 +7285,7 @@
         <v>0</v>
       </c>
       <c r="BJ25" t="n">
-        <v>0</v>
+        <v>433</v>
       </c>
       <c r="BK25" t="n">
         <v>0</v>
@@ -6952,10 +7312,10 @@
         <v>0</v>
       </c>
       <c r="BS25" t="n">
-        <v>415567048200</v>
+        <v>0</v>
       </c>
       <c r="BT25" t="n">
-        <v>0</v>
+        <v>251396069121</v>
       </c>
       <c r="BU25" t="n">
         <v>0</v>
@@ -6967,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="BX25" t="n">
-        <v>0</v>
+        <v>433</v>
       </c>
       <c r="BY25" t="n">
         <v>0</v>
@@ -6991,6 +7351,25 @@
         <v>0</v>
       </c>
       <c r="CF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH25" t="n">
+        <v>1393</v>
+      </c>
+      <c r="CI25" t="inlineStr"/>
+      <c r="CJ25" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="CK25" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="CL25" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="CM25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7001,10 +7380,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7141738000</v>
+        <v>16515926741</v>
       </c>
       <c r="C26" t="n">
-        <v>1611400</v>
+        <v>5913766</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -7046,7 +7425,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>5208</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -7055,19 +7434,19 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1670.67</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1923</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1670.67</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>6932787</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>197471571</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -7079,16 +7458,16 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>11919229.33</v>
       </c>
       <c r="AD26" t="n">
-        <v>13058256400</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>7725120726</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -7097,19 +7476,19 @@
         <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>609</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1529.33</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>608.33</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>2524652</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>72072593.67</v>
       </c>
       <c r="AM26" t="n">
         <v>0</v>
@@ -7121,10 +7500,10 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>622968</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>5396966.67</v>
       </c>
       <c r="AR26" t="n">
         <v>0</v>
@@ -7136,19 +7515,19 @@
         <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>36.67</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>26370</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>78858</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>2448458.33</v>
       </c>
       <c r="AZ26" t="n">
         <v>0</v>
@@ -7163,13 +7542,13 @@
         <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>17845041.67</v>
       </c>
       <c r="BE26" t="n">
-        <v>43621138600</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>29359083093</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -7178,19 +7557,19 @@
         <v>0</v>
       </c>
       <c r="BI26" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0</v>
+        <v>4435</v>
       </c>
       <c r="BK26" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BL26" t="n">
-        <v>0</v>
+        <v>84154</v>
       </c>
       <c r="BM26" t="n">
-        <v>0</v>
+        <v>2509116</v>
       </c>
       <c r="BN26" t="n">
         <v>0</v>
@@ -7205,13 +7584,13 @@
         <v>0</v>
       </c>
       <c r="BR26" t="n">
-        <v>0</v>
+        <v>2660414</v>
       </c>
       <c r="BS26" t="n">
-        <v>433342650000</v>
+        <v>0</v>
       </c>
       <c r="BT26" t="n">
-        <v>0</v>
+        <v>291730405461</v>
       </c>
       <c r="BU26" t="n">
         <v>0</v>
@@ -7220,19 +7599,19 @@
         <v>0</v>
       </c>
       <c r="BW26" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BX26" t="n">
-        <v>0</v>
+        <v>4435</v>
       </c>
       <c r="BY26" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BZ26" t="n">
-        <v>0</v>
+        <v>84154</v>
       </c>
       <c r="CA26" t="n">
-        <v>0</v>
+        <v>2509116</v>
       </c>
       <c r="CB26" t="n">
         <v>0</v>
@@ -7247,8 +7626,17 @@
         <v>0</v>
       </c>
       <c r="CF26" t="n">
-        <v>0</v>
-      </c>
+        <v>2660414</v>
+      </c>
+      <c r="CG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH26" t="inlineStr"/>
+      <c r="CI26" t="inlineStr"/>
+      <c r="CJ26" t="inlineStr"/>
+      <c r="CK26" t="inlineStr"/>
+      <c r="CL26" t="inlineStr"/>
+      <c r="CM26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -7257,10 +7645,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7092235500</v>
+        <v>17681087942</v>
       </c>
       <c r="C27" t="n">
-        <v>1979200</v>
+        <v>5466964</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -7301,9 +7689,7 @@
       <c r="P27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -7311,19 +7697,19 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1670.67</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1923</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1670.67</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>6932787.33</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>194920730.67</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -7335,16 +7721,16 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>11911778.67</v>
       </c>
       <c r="AD27" t="n">
-        <v>11567732400</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>6436735918</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -7353,19 +7739,19 @@
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>609</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1529.33</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>608.33</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>2523955.33</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>71505717.33</v>
       </c>
       <c r="AM27" t="n">
         <v>0</v>
@@ -7377,10 +7763,10 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>622968</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>5410855.33</v>
       </c>
       <c r="AR27" t="n">
         <v>0</v>
@@ -7392,19 +7778,19 @@
         <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>35.67</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>26371</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>71517</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>2182651.33</v>
       </c>
       <c r="AZ27" t="n">
         <v>0</v>
@@ -7419,13 +7805,13 @@
         <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>20087595.67</v>
       </c>
       <c r="BE27" t="n">
-        <v>30842460000</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>21454429781</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -7434,19 +7820,19 @@
         <v>0</v>
       </c>
       <c r="BI27" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BJ27" t="n">
-        <v>0</v>
+        <v>4435</v>
       </c>
       <c r="BK27" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BL27" t="n">
-        <v>0</v>
+        <v>84154</v>
       </c>
       <c r="BM27" t="n">
-        <v>0</v>
+        <v>2383390</v>
       </c>
       <c r="BN27" t="n">
         <v>0</v>
@@ -7461,13 +7847,13 @@
         <v>0</v>
       </c>
       <c r="BR27" t="n">
-        <v>0</v>
+        <v>3200681</v>
       </c>
       <c r="BS27" t="n">
-        <v>405453973500</v>
+        <v>0</v>
       </c>
       <c r="BT27" t="n">
-        <v>0</v>
+        <v>277049972646</v>
       </c>
       <c r="BU27" t="n">
         <v>0</v>
@@ -7476,19 +7862,19 @@
         <v>0</v>
       </c>
       <c r="BW27" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BX27" t="n">
-        <v>0</v>
+        <v>4435</v>
       </c>
       <c r="BY27" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BZ27" t="n">
-        <v>0</v>
+        <v>84154</v>
       </c>
       <c r="CA27" t="n">
-        <v>0</v>
+        <v>2383390</v>
       </c>
       <c r="CB27" t="n">
         <v>0</v>
@@ -7503,8 +7889,19 @@
         <v>0</v>
       </c>
       <c r="CF27" t="n">
-        <v>0</v>
-      </c>
+        <v>3200681</v>
+      </c>
+      <c r="CG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH27" t="n">
+        <v>1376</v>
+      </c>
+      <c r="CI27" t="inlineStr"/>
+      <c r="CJ27" t="inlineStr"/>
+      <c r="CK27" t="inlineStr"/>
+      <c r="CL27" t="inlineStr"/>
+      <c r="CM27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -7513,10 +7910,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7053882200</v>
+        <v>18958442556</v>
       </c>
       <c r="C28" t="n">
-        <v>1635100</v>
+        <v>5861617</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -7557,9 +7954,7 @@
       <c r="P28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -7567,19 +7962,19 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1670.67</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1923</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1670.67</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>6932787.33</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>196471570</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -7591,16 +7986,16 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>11911778.67</v>
       </c>
       <c r="AD28" t="n">
-        <v>11962559800</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>6496382514</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -7609,19 +8004,19 @@
         <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>746.67</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>2523252</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>71324295.33</v>
       </c>
       <c r="AM28" t="n">
         <v>0</v>
@@ -7633,10 +8028,10 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>622968</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>4328631</v>
       </c>
       <c r="AR28" t="n">
         <v>0</v>
@@ -7648,19 +8043,19 @@
         <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>1922</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>9821</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>373462.33</v>
       </c>
       <c r="AZ28" t="n">
         <v>0</v>
@@ -7675,13 +8070,13 @@
         <v>0</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>9821</v>
       </c>
       <c r="BE28" t="n">
-        <v>1148772500</v>
+        <v>0</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>717916974</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -7690,19 +8085,19 @@
         <v>0</v>
       </c>
       <c r="BI28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="BK28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BL28" t="n">
-        <v>0</v>
+        <v>37881</v>
       </c>
       <c r="BM28" t="n">
-        <v>0</v>
+        <v>1136726</v>
       </c>
       <c r="BN28" t="n">
         <v>0</v>
@@ -7717,13 +8112,13 @@
         <v>0</v>
       </c>
       <c r="BR28" t="n">
-        <v>0</v>
+        <v>37881</v>
       </c>
       <c r="BS28" t="n">
-        <v>384569415700</v>
+        <v>0</v>
       </c>
       <c r="BT28" t="n">
-        <v>0</v>
+        <v>250283185524</v>
       </c>
       <c r="BU28" t="n">
         <v>0</v>
@@ -7732,19 +8127,19 @@
         <v>0</v>
       </c>
       <c r="BW28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BX28" t="n">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="BY28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BZ28" t="n">
-        <v>0</v>
+        <v>37881</v>
       </c>
       <c r="CA28" t="n">
-        <v>0</v>
+        <v>1136726</v>
       </c>
       <c r="CB28" t="n">
         <v>0</v>
@@ -7759,8 +8154,19 @@
         <v>0</v>
       </c>
       <c r="CF28" t="n">
-        <v>0</v>
-      </c>
+        <v>37881</v>
+      </c>
+      <c r="CG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH28" t="inlineStr"/>
+      <c r="CI28" t="n">
+        <v>1632</v>
+      </c>
+      <c r="CJ28" t="inlineStr"/>
+      <c r="CK28" t="inlineStr"/>
+      <c r="CL28" t="inlineStr"/>
+      <c r="CM28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7769,10 +8175,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6902849900</v>
+        <v>17612459974</v>
       </c>
       <c r="C29" t="n">
-        <v>1605000</v>
+        <v>5881079</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -7813,9 +8219,7 @@
       <c r="P29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -7823,19 +8227,19 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1670.67</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1923</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1670.67</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>6932787.33</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>195124875.67</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -7847,16 +8251,16 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>11911778.67</v>
       </c>
       <c r="AD29" t="n">
-        <v>12058833400</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>6459110601</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -7865,19 +8269,19 @@
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>609</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1529.33</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>608.33</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>2523955.33</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>71493004</v>
       </c>
       <c r="AM29" t="n">
         <v>0</v>
@@ -7889,10 +8293,10 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>622968</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>5410855.33</v>
       </c>
       <c r="AR29" t="n">
         <v>0</v>
@@ -7904,19 +8308,19 @@
         <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>35.67</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>26371</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>71517</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>2134730</v>
       </c>
       <c r="AZ29" t="n">
         <v>0</v>
@@ -7931,13 +8335,13 @@
         <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>20087595.67</v>
       </c>
       <c r="BE29" t="n">
-        <v>32317200700</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>21761840337</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -7946,19 +8350,19 @@
         <v>0</v>
       </c>
       <c r="BI29" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0</v>
+        <v>4435</v>
       </c>
       <c r="BK29" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BL29" t="n">
-        <v>0</v>
+        <v>84154</v>
       </c>
       <c r="BM29" t="n">
-        <v>0</v>
+        <v>2109440</v>
       </c>
       <c r="BN29" t="n">
         <v>0</v>
@@ -7973,13 +8377,13 @@
         <v>0</v>
       </c>
       <c r="BR29" t="n">
-        <v>0</v>
+        <v>3200681</v>
       </c>
       <c r="BS29" t="n">
-        <v>445829984100</v>
+        <v>0</v>
       </c>
       <c r="BT29" t="n">
-        <v>0</v>
+        <v>276920621048</v>
       </c>
       <c r="BU29" t="n">
         <v>0</v>
@@ -7988,19 +8392,19 @@
         <v>0</v>
       </c>
       <c r="BW29" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BX29" t="n">
-        <v>0</v>
+        <v>4435</v>
       </c>
       <c r="BY29" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BZ29" t="n">
-        <v>0</v>
+        <v>84154</v>
       </c>
       <c r="CA29" t="n">
-        <v>0</v>
+        <v>2109440</v>
       </c>
       <c r="CB29" t="n">
         <v>0</v>
@@ -8015,6 +8419,25 @@
         <v>0</v>
       </c>
       <c r="CF29" t="n">
+        <v>3200681</v>
+      </c>
+      <c r="CG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH29" t="n">
+        <v>8832</v>
+      </c>
+      <c r="CI29" t="inlineStr"/>
+      <c r="CJ29" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="CK29" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="CL29" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="CM29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8025,10 +8448,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7038765100</v>
+        <v>18799682131</v>
       </c>
       <c r="C30" t="n">
-        <v>1765600</v>
+        <v>5820316</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -8069,9 +8492,7 @@
       <c r="P30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -8079,19 +8500,19 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1670.67</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1923</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1670.67</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>6932787.33</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>195393567.33</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -8103,16 +8524,16 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>11911778.67</v>
       </c>
       <c r="AD30" t="n">
-        <v>11991132900</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>6511018623</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -8121,19 +8542,19 @@
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>748.67</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>2523252</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>71624524.33</v>
       </c>
       <c r="AM30" t="n">
         <v>0</v>
@@ -8145,10 +8566,10 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>622968</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>4333346.33</v>
       </c>
       <c r="AR30" t="n">
         <v>0</v>
@@ -8160,19 +8581,19 @@
         <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>1964.67</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>9821</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>289130.33</v>
       </c>
       <c r="AZ30" t="n">
         <v>0</v>
@@ -8187,13 +8608,13 @@
         <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>58046.33</v>
       </c>
       <c r="BE30" t="n">
-        <v>1345783500</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>858062353</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -8202,19 +8623,19 @@
         <v>0</v>
       </c>
       <c r="BI30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BJ30" t="n">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="BK30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BL30" t="n">
-        <v>0</v>
+        <v>37881</v>
       </c>
       <c r="BM30" t="n">
-        <v>0</v>
+        <v>1196718</v>
       </c>
       <c r="BN30" t="n">
         <v>0</v>
@@ -8229,13 +8650,13 @@
         <v>0</v>
       </c>
       <c r="BR30" t="n">
-        <v>0</v>
+        <v>37881</v>
       </c>
       <c r="BS30" t="n">
-        <v>410894120500</v>
+        <v>0</v>
       </c>
       <c r="BT30" t="n">
-        <v>0</v>
+        <v>250464180593</v>
       </c>
       <c r="BU30" t="n">
         <v>0</v>
@@ -8244,19 +8665,19 @@
         <v>0</v>
       </c>
       <c r="BW30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BX30" t="n">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="BY30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BZ30" t="n">
-        <v>0</v>
+        <v>37881</v>
       </c>
       <c r="CA30" t="n">
-        <v>0</v>
+        <v>1196718</v>
       </c>
       <c r="CB30" t="n">
         <v>0</v>
@@ -8271,6 +8692,25 @@
         <v>0</v>
       </c>
       <c r="CF30" t="n">
+        <v>37881</v>
+      </c>
+      <c r="CG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH30" t="n">
+        <v>9376</v>
+      </c>
+      <c r="CI30" t="inlineStr"/>
+      <c r="CJ30" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="CK30" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="CL30" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="CM30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8281,10 +8721,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7219716400</v>
+        <v>19079572072</v>
       </c>
       <c r="C31" t="n">
-        <v>1626400</v>
+        <v>5782063</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -8325,9 +8765,7 @@
       <c r="P31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -8335,19 +8773,19 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1670.67</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1923</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1670.67</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>6932787.33</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>196218519.33</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -8359,16 +8797,16 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>11911778.67</v>
       </c>
       <c r="AD31" t="n">
-        <v>13349375300</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>6481218335</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -8377,19 +8815,19 @@
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>683.67</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>2523252</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>71568479</v>
       </c>
       <c r="AM31" t="n">
         <v>0</v>
@@ -8401,10 +8839,10 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>622968</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>4303460</v>
       </c>
       <c r="AR31" t="n">
         <v>0</v>
@@ -8446,10 +8884,10 @@
         <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1090330700</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>692875899</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -8488,10 +8926,10 @@
         <v>0</v>
       </c>
       <c r="BS31" t="n">
-        <v>386504410000</v>
+        <v>0</v>
       </c>
       <c r="BT31" t="n">
-        <v>0</v>
+        <v>250421255223</v>
       </c>
       <c r="BU31" t="n">
         <v>0</v>
@@ -8529,6 +8967,17 @@
       <c r="CF31" t="n">
         <v>0</v>
       </c>
+      <c r="CG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH31" t="n">
+        <v>1328</v>
+      </c>
+      <c r="CI31" t="inlineStr"/>
+      <c r="CJ31" t="inlineStr"/>
+      <c r="CK31" t="inlineStr"/>
+      <c r="CL31" t="inlineStr"/>
+      <c r="CM31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -8537,10 +8986,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7212156600</v>
+        <v>19491965285</v>
       </c>
       <c r="C32" t="n">
-        <v>1636700</v>
+        <v>5798306</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -8581,9 +9030,7 @@
       <c r="P32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -8591,19 +9038,19 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1670.67</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1923</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1670.67</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>6932787.33</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>194928138.33</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -8615,16 +9062,16 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>11911778.67</v>
       </c>
       <c r="AD32" t="n">
-        <v>13670061600</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>6503032312</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -8633,19 +9080,19 @@
         <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>609</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1529.33</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>608.33</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>2523955.33</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>71335199.33</v>
       </c>
       <c r="AM32" t="n">
         <v>0</v>
@@ -8657,10 +9104,10 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>622968</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>5410855.33</v>
       </c>
       <c r="AR32" t="n">
         <v>0</v>
@@ -8672,19 +9119,19 @@
         <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>35.67</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>26371</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>71517</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>2083193.33</v>
       </c>
       <c r="AZ32" t="n">
         <v>0</v>
@@ -8699,13 +9146,13 @@
         <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>20087595.67</v>
       </c>
       <c r="BE32" t="n">
-        <v>39015560000</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>22404583749</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -8714,19 +9161,19 @@
         <v>0</v>
       </c>
       <c r="BI32" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BJ32" t="n">
-        <v>0</v>
+        <v>4435</v>
       </c>
       <c r="BK32" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BL32" t="n">
-        <v>0</v>
+        <v>84154</v>
       </c>
       <c r="BM32" t="n">
-        <v>0</v>
+        <v>2232711</v>
       </c>
       <c r="BN32" t="n">
         <v>0</v>
@@ -8741,13 +9188,13 @@
         <v>0</v>
       </c>
       <c r="BR32" t="n">
-        <v>0</v>
+        <v>3200681</v>
       </c>
       <c r="BS32" t="n">
-        <v>439995924700</v>
+        <v>0</v>
       </c>
       <c r="BT32" t="n">
-        <v>0</v>
+        <v>273816225052</v>
       </c>
       <c r="BU32" t="n">
         <v>0</v>
@@ -8756,19 +9203,19 @@
         <v>0</v>
       </c>
       <c r="BW32" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BX32" t="n">
-        <v>0</v>
+        <v>4435</v>
       </c>
       <c r="BY32" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BZ32" t="n">
-        <v>0</v>
+        <v>84154</v>
       </c>
       <c r="CA32" t="n">
-        <v>0</v>
+        <v>2232711</v>
       </c>
       <c r="CB32" t="n">
         <v>0</v>
@@ -8783,7 +9230,26 @@
         <v>0</v>
       </c>
       <c r="CF32" t="n">
-        <v>0</v>
+        <v>3200681</v>
+      </c>
+      <c r="CG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH32" t="n">
+        <v>1659</v>
+      </c>
+      <c r="CI32" t="inlineStr"/>
+      <c r="CJ32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CK32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CL32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CM32" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="33">
@@ -8793,10 +9259,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7087309800</v>
+        <v>19325531280</v>
       </c>
       <c r="C33" t="n">
-        <v>1843600</v>
+        <v>4595126</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -8837,9 +9303,7 @@
       <c r="P33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -8847,19 +9311,19 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1670.67</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1923</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1670.67</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>6932787.33</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>195421150</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -8871,16 +9335,16 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>11911778.67</v>
       </c>
       <c r="AD33" t="n">
-        <v>12168184500</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>6526356477</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -8889,19 +9353,19 @@
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>889</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>2523252</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>71679664.33</v>
       </c>
       <c r="AM33" t="n">
         <v>0</v>
@@ -8913,10 +9377,10 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>622968</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>4422357</v>
       </c>
       <c r="AR33" t="n">
         <v>0</v>
@@ -8928,19 +9392,19 @@
         <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>6643.67</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>19636.67</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>604659.67</v>
       </c>
       <c r="AZ33" t="n">
         <v>0</v>
@@ -8955,13 +9419,13 @@
         <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>520629.33</v>
       </c>
       <c r="BE33" t="n">
-        <v>2401978100</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1745227203</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -8970,19 +9434,19 @@
         <v>0</v>
       </c>
       <c r="BI33" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BJ33" t="n">
-        <v>0</v>
+        <v>599</v>
       </c>
       <c r="BK33" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BL33" t="n">
-        <v>0</v>
+        <v>37881</v>
       </c>
       <c r="BM33" t="n">
-        <v>0</v>
+        <v>1132847</v>
       </c>
       <c r="BN33" t="n">
         <v>0</v>
@@ -8997,13 +9461,13 @@
         <v>0</v>
       </c>
       <c r="BR33" t="n">
-        <v>0</v>
+        <v>37881</v>
       </c>
       <c r="BS33" t="n">
-        <v>387716344600</v>
+        <v>0</v>
       </c>
       <c r="BT33" t="n">
-        <v>0</v>
+        <v>250833424296</v>
       </c>
       <c r="BU33" t="n">
         <v>0</v>
@@ -9012,19 +9476,19 @@
         <v>0</v>
       </c>
       <c r="BW33" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BX33" t="n">
-        <v>0</v>
+        <v>599</v>
       </c>
       <c r="BY33" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BZ33" t="n">
-        <v>0</v>
+        <v>37881</v>
       </c>
       <c r="CA33" t="n">
-        <v>0</v>
+        <v>1132847</v>
       </c>
       <c r="CB33" t="n">
         <v>0</v>
@@ -9039,6 +9503,25 @@
         <v>0</v>
       </c>
       <c r="CF33" t="n">
+        <v>37881</v>
+      </c>
+      <c r="CG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH33" t="n">
+        <v>1941</v>
+      </c>
+      <c r="CI33" t="inlineStr"/>
+      <c r="CJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9049,10 +9532,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7225339600</v>
+        <v>19693888058</v>
       </c>
       <c r="C34" t="n">
-        <v>1667800</v>
+        <v>5841567</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -9093,9 +9576,7 @@
       <c r="P34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -9103,19 +9584,19 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1670.67</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1923</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1670.67</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>6932787.33</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>195823869.33</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
@@ -9127,16 +9608,16 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>11911778.67</v>
       </c>
       <c r="AD34" t="n">
-        <v>12467225100</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>6543758130</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -9145,19 +9626,19 @@
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>609</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1529.33</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>608.33</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2523955.33</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>71139433.67</v>
       </c>
       <c r="AM34" t="n">
         <v>0</v>
@@ -9169,10 +9650,10 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>622968</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>5410855.33</v>
       </c>
       <c r="AR34" t="n">
         <v>0</v>
@@ -9184,19 +9665,19 @@
         <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>35.67</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>26371</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>71517</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>2275256.67</v>
       </c>
       <c r="AZ34" t="n">
         <v>0</v>
@@ -9211,13 +9692,13 @@
         <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>20087595.67</v>
       </c>
       <c r="BE34" t="n">
-        <v>32202687000</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>23089773244</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -9226,19 +9707,19 @@
         <v>0</v>
       </c>
       <c r="BI34" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BJ34" t="n">
-        <v>0</v>
+        <v>4435</v>
       </c>
       <c r="BK34" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BL34" t="n">
-        <v>0</v>
+        <v>84154</v>
       </c>
       <c r="BM34" t="n">
-        <v>0</v>
+        <v>2393564</v>
       </c>
       <c r="BN34" t="n">
         <v>0</v>
@@ -9253,13 +9734,13 @@
         <v>0</v>
       </c>
       <c r="BR34" t="n">
-        <v>0</v>
+        <v>3200681</v>
       </c>
       <c r="BS34" t="n">
-        <v>420297239900</v>
+        <v>0</v>
       </c>
       <c r="BT34" t="n">
-        <v>0</v>
+        <v>273968861507</v>
       </c>
       <c r="BU34" t="n">
         <v>0</v>
@@ -9268,19 +9749,19 @@
         <v>0</v>
       </c>
       <c r="BW34" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BX34" t="n">
-        <v>0</v>
+        <v>4435</v>
       </c>
       <c r="BY34" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BZ34" t="n">
-        <v>0</v>
+        <v>84154</v>
       </c>
       <c r="CA34" t="n">
-        <v>0</v>
+        <v>2393564</v>
       </c>
       <c r="CB34" t="n">
         <v>0</v>
@@ -9295,7 +9776,26 @@
         <v>0</v>
       </c>
       <c r="CF34" t="n">
-        <v>0</v>
+        <v>3200681</v>
+      </c>
+      <c r="CG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH34" t="n">
+        <v>1099</v>
+      </c>
+      <c r="CI34" t="inlineStr"/>
+      <c r="CJ34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CK34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CL34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CM34" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="35">
@@ -9305,10 +9805,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7254445400</v>
+        <v>16330124504</v>
       </c>
       <c r="C35" t="n">
-        <v>1603100</v>
+        <v>5863564</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -9349,9 +9849,7 @@
       <c r="P35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -9359,19 +9857,19 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1670.67</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1923</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1670.67</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>6932787.33</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>194946490</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -9383,16 +9881,16 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>11911778.67</v>
       </c>
       <c r="AD35" t="n">
-        <v>13193813000</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>6521082897</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -9401,19 +9899,19 @@
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>894</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>2523252</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>71077872.33</v>
       </c>
       <c r="AM35" t="n">
         <v>0</v>
@@ -9425,10 +9923,10 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>622968</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>4433993.67</v>
       </c>
       <c r="AR35" t="n">
         <v>0</v>
@@ -9440,19 +9938,19 @@
         <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>6739</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>19636.67</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>577337</v>
       </c>
       <c r="AZ35" t="n">
         <v>0</v>
@@ -9467,13 +9965,13 @@
         <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>640278</v>
       </c>
       <c r="BE35" t="n">
-        <v>3069858900</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1852832155</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -9482,19 +9980,19 @@
         <v>0</v>
       </c>
       <c r="BI35" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BJ35" t="n">
-        <v>0</v>
+        <v>602</v>
       </c>
       <c r="BK35" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BL35" t="n">
-        <v>0</v>
+        <v>37881</v>
       </c>
       <c r="BM35" t="n">
-        <v>0</v>
+        <v>1136031</v>
       </c>
       <c r="BN35" t="n">
         <v>0</v>
@@ -9509,13 +10007,13 @@
         <v>0</v>
       </c>
       <c r="BR35" t="n">
-        <v>0</v>
+        <v>37881</v>
       </c>
       <c r="BS35" t="n">
-        <v>388801380600</v>
+        <v>0</v>
       </c>
       <c r="BT35" t="n">
-        <v>0</v>
+        <v>259704848530</v>
       </c>
       <c r="BU35" t="n">
         <v>0</v>
@@ -9524,19 +10022,19 @@
         <v>0</v>
       </c>
       <c r="BW35" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BX35" t="n">
-        <v>0</v>
+        <v>602</v>
       </c>
       <c r="BY35" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BZ35" t="n">
-        <v>0</v>
+        <v>37881</v>
       </c>
       <c r="CA35" t="n">
-        <v>0</v>
+        <v>1136031</v>
       </c>
       <c r="CB35" t="n">
         <v>0</v>
@@ -9551,7 +10049,26 @@
         <v>0</v>
       </c>
       <c r="CF35" t="n">
-        <v>0</v>
+        <v>37881</v>
+      </c>
+      <c r="CG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH35" t="n">
+        <v>1183</v>
+      </c>
+      <c r="CI35" t="inlineStr"/>
+      <c r="CJ35" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="CK35" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="CL35" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="CM35" t="n">
+        <v>0.0028</v>
       </c>
     </row>
     <row r="36">
@@ -9561,10 +10078,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7283821800</v>
+        <v>19573227904</v>
       </c>
       <c r="C36" t="n">
-        <v>1815600</v>
+        <v>5876013</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -9605,9 +10122,7 @@
       <c r="P36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -9615,19 +10130,19 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1670.67</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1923</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1670.67</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>6932787.33</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>195888527</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -9639,16 +10154,16 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>11911778.67</v>
       </c>
       <c r="AD36" t="n">
-        <v>13133210900</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>6522965403</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -9657,19 +10172,19 @@
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>609</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1529.33</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>608.33</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>2523955.33</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>71425880.67</v>
       </c>
       <c r="AM36" t="n">
         <v>0</v>
@@ -9681,10 +10196,10 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>622968</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>5410855.33</v>
       </c>
       <c r="AR36" t="n">
         <v>0</v>
@@ -9696,19 +10211,19 @@
         <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>35.67</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>26371</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>71517</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>2250967</v>
       </c>
       <c r="AZ36" t="n">
         <v>0</v>
@@ -9723,13 +10238,13 @@
         <v>0</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>20087595.67</v>
       </c>
       <c r="BE36" t="n">
-        <v>39568790800</v>
+        <v>0</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>22525381995</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -9738,19 +10253,19 @@
         <v>0</v>
       </c>
       <c r="BI36" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BJ36" t="n">
-        <v>0</v>
+        <v>4435</v>
       </c>
       <c r="BK36" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BL36" t="n">
-        <v>0</v>
+        <v>84154</v>
       </c>
       <c r="BM36" t="n">
-        <v>0</v>
+        <v>2476732</v>
       </c>
       <c r="BN36" t="n">
         <v>0</v>
@@ -9765,13 +10280,13 @@
         <v>0</v>
       </c>
       <c r="BR36" t="n">
-        <v>0</v>
+        <v>3200681</v>
       </c>
       <c r="BS36" t="n">
-        <v>428652350300</v>
+        <v>0</v>
       </c>
       <c r="BT36" t="n">
-        <v>0</v>
+        <v>273937637647</v>
       </c>
       <c r="BU36" t="n">
         <v>0</v>
@@ -9780,19 +10295,19 @@
         <v>0</v>
       </c>
       <c r="BW36" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BX36" t="n">
-        <v>0</v>
+        <v>4435</v>
       </c>
       <c r="BY36" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BZ36" t="n">
-        <v>0</v>
+        <v>84154</v>
       </c>
       <c r="CA36" t="n">
-        <v>0</v>
+        <v>2476732</v>
       </c>
       <c r="CB36" t="n">
         <v>0</v>
@@ -9807,7 +10322,26 @@
         <v>0</v>
       </c>
       <c r="CF36" t="n">
-        <v>0</v>
+        <v>3200681</v>
+      </c>
+      <c r="CG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH36" t="n">
+        <v>1379</v>
+      </c>
+      <c r="CI36" t="inlineStr"/>
+      <c r="CJ36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CK36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CL36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CM36" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="37">
@@ -9817,10 +10351,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7003426600</v>
+        <v>18857707074</v>
       </c>
       <c r="C37" t="n">
-        <v>1995400</v>
+        <v>5923461</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -9861,9 +10395,7 @@
       <c r="P37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -9871,19 +10403,19 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>1670.67</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1923</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1670.67</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>6932787.33</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>194071255.33</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -9895,16 +10427,16 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1713333.33</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>11911778.67</v>
       </c>
       <c r="AD37" t="n">
-        <v>12063758600</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>6561483623</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -9913,19 +10445,19 @@
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>890.33</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>2523252</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>71237524.33</v>
       </c>
       <c r="AM37" t="n">
         <v>0</v>
@@ -9937,10 +10469,10 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>622968</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>4426064.67</v>
       </c>
       <c r="AR37" t="n">
         <v>0</v>
@@ -9952,19 +10484,19 @@
         <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>6678.33</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>19636.67</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>597611</v>
       </c>
       <c r="AZ37" t="n">
         <v>0</v>
@@ -9979,13 +10511,13 @@
         <v>0</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>570471.33</v>
       </c>
       <c r="BE37" t="n">
-        <v>2418101300</v>
+        <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1887705961</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -9994,19 +10526,19 @@
         <v>0</v>
       </c>
       <c r="BI37" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BJ37" t="n">
-        <v>0</v>
+        <v>599</v>
       </c>
       <c r="BK37" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BL37" t="n">
-        <v>0</v>
+        <v>37881</v>
       </c>
       <c r="BM37" t="n">
-        <v>0</v>
+        <v>1242111</v>
       </c>
       <c r="BN37" t="n">
         <v>0</v>
@@ -10021,13 +10553,13 @@
         <v>0</v>
       </c>
       <c r="BR37" t="n">
-        <v>0</v>
+        <v>37881</v>
       </c>
       <c r="BS37" t="n">
-        <v>412058790500</v>
+        <v>0</v>
       </c>
       <c r="BT37" t="n">
-        <v>0</v>
+        <v>251737800733</v>
       </c>
       <c r="BU37" t="n">
         <v>0</v>
@@ -10036,19 +10568,19 @@
         <v>0</v>
       </c>
       <c r="BW37" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BX37" t="n">
-        <v>0</v>
+        <v>599</v>
       </c>
       <c r="BY37" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BZ37" t="n">
-        <v>0</v>
+        <v>37881</v>
       </c>
       <c r="CA37" t="n">
-        <v>0</v>
+        <v>1242111</v>
       </c>
       <c r="CB37" t="n">
         <v>0</v>
@@ -10063,6 +10595,25 @@
         <v>0</v>
       </c>
       <c r="CF37" t="n">
+        <v>37881</v>
+      </c>
+      <c r="CG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH37" t="n">
+        <v>1569</v>
+      </c>
+      <c r="CI37" t="inlineStr"/>
+      <c r="CJ37" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="CK37" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="CL37" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="CM37" t="n">
         <v>0</v>
       </c>
     </row>
